--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,12 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105806</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7450,10 +7445,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>505239.131624698</v>
+        <v>505239</v>
       </c>
       <c r="R57" t="n">
-        <v>6338019.505236985</v>
+        <v>6338020</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -7483,19 +7478,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7539,12 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98590</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7576,10 +7556,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>505239.131624698</v>
+        <v>505239</v>
       </c>
       <c r="R58" t="n">
-        <v>6338019.505236985</v>
+        <v>6338020</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7609,19 +7589,9 @@
           <t>1995-08-01</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>1995-08-01</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,7 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>105806</v>
+        <v>105815</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,7 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>105815</v>
+        <v>105820</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,7 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>105820</v>
+        <v>105848</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,7 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>105848</v>
+        <v>105854</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,7 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>105854</v>
+        <v>105861</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98627</v>
+        <v>98634</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,7 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>105861</v>
+        <v>105865</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98634</v>
+        <v>98638</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,7 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>105865</v>
+        <v>105872</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98638</v>
+        <v>98645</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,7 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>105875</v>
+        <v>105880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98648</v>
+        <v>98653</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,7 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>105880</v>
+        <v>105888</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98653</v>
+        <v>98661</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -7417,7 +7417,7 @@
         <v>74437154</v>
       </c>
       <c r="B57" t="n">
-        <v>105888</v>
+        <v>105898</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 41968-2023 artfynd.xlsx
+++ b/artfynd/A 41968-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13368975</v>
+        <v>284575</v>
       </c>
       <c r="B2" t="n">
-        <v>44174</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102421</v>
+        <v>793</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåttergubbemal</t>
+          <t>Fagervaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Digitivalva arnicella</t>
+          <t>Hygrocybe aurantiosplendens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(von Heyden, 1863)</t>
+          <t>R.Haller Aar.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>mina</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505222.8144014849</v>
+        <v>505191</v>
       </c>
       <c r="R2" t="n">
-        <v>6338041.161264331</v>
+        <v>6338060</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,9 +768,10 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ohävdad betesmark</t>
-        </is>
-      </c>
+          <t>Ohävdad ängsmark</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -794,49 +780,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>263733</v>
+        <v>301907</v>
       </c>
       <c r="B3" t="n">
-        <v>86159</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Trådvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
+          <t>Hygrocybe intermedia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kühner) Singer</t>
+          <t>(Pass.) Fayod</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505219.0224022623</v>
+        <v>505204</v>
       </c>
       <c r="R3" t="n">
-        <v>6338034.111531877</v>
+        <v>6338082</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +880,9 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Ohävdad.</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+          <t>Ohävdad ängsmark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -921,44 +891,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>327762</v>
+        <v>301908</v>
       </c>
       <c r="B4" t="n">
-        <v>86156</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Trådvaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Hygrocybe intermedia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>(Pass.) Fayod</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505209.7470439128</v>
+        <v>505203</v>
       </c>
       <c r="R4" t="n">
-        <v>6338069.324315643</v>
+        <v>6338058</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,22 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +991,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Ohävdad.</t>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1047,54 +1002,49 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>594127</v>
+        <v>314697</v>
       </c>
       <c r="B5" t="n">
-        <v>102160</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1560</v>
+        <v>804</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sepiavaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Neohygrocybe ovina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bull.) Herink</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1103,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505147.2299755766</v>
+        <v>505191</v>
       </c>
       <c r="R5" t="n">
-        <v>6338128.313888484</v>
+        <v>6338053</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,22 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,14 +1100,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Artificiell miljö</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>vägkant</t>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,22 +1113,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13380116</v>
+        <v>327762</v>
       </c>
       <c r="B6" t="n">
-        <v>44334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,27 +1131,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102021</v>
+        <v>805</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1230,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505178.7975747958</v>
+        <v>505210</v>
       </c>
       <c r="R6" t="n">
-        <v>6338068.743390153</v>
+        <v>6338069</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1260,22 +1194,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,6 +1210,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Ohävdad.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1302,53 +1231,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1549630</v>
+        <v>327984</v>
       </c>
       <c r="B7" t="n">
-        <v>86135</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4379</v>
+        <v>805</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505178.7975747958</v>
+        <v>505182</v>
       </c>
       <c r="R7" t="n">
-        <v>6338068.743390153</v>
+        <v>6338047</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,22 +1305,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,7 +1324,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Ohävdad.</t>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,22 +1335,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2649255</v>
+        <v>328191</v>
       </c>
       <c r="B8" t="n">
-        <v>106756</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,37 +1353,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220228</v>
+        <v>805</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505178.7975747958</v>
+        <v>505192</v>
       </c>
       <c r="R8" t="n">
-        <v>6338068.743390153</v>
+        <v>6338094</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,22 +1416,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,7 +1435,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Ohävdad.</t>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1529,22 +1446,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2674357</v>
+        <v>329371</v>
       </c>
       <c r="B9" t="n">
-        <v>101690</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,37 +1464,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220164</v>
+        <v>805</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505178.7975747958</v>
+        <v>505204</v>
       </c>
       <c r="R9" t="n">
-        <v>6338068.743390153</v>
+        <v>6338084</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1606,22 +1527,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1546,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Ohävdad.</t>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1646,39 +1557,34 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1686351</v>
+        <v>329372</v>
       </c>
       <c r="B10" t="n">
-        <v>86149</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4388</v>
+        <v>805</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mönjevaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrocybe miniata</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1686,20 +1592,29 @@
           <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505178.7975747958</v>
+        <v>505138</v>
       </c>
       <c r="R10" t="n">
-        <v>6338068.743390153</v>
+        <v>6338121</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,22 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,7 +1657,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Ohävdad.</t>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1763,56 +1668,64 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1209179</v>
+        <v>329374</v>
       </c>
       <c r="B11" t="n">
-        <v>86111</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4393</v>
+        <v>805</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling/rödgrön vaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505178.7975747958</v>
+        <v>505183</v>
       </c>
       <c r="R11" t="n">
-        <v>6338068.743390153</v>
+        <v>6338064</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1836,22 +1749,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,7 +1768,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Ohävdad.</t>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1876,60 +1779,64 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6673484</v>
+        <v>329375</v>
       </c>
       <c r="B12" t="n">
-        <v>86129</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>239209</v>
+        <v>805</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kantarellvaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505178.7975747958</v>
+        <v>505112</v>
       </c>
       <c r="R12" t="n">
-        <v>6338068.743390153</v>
+        <v>6338021</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1953,22 +1860,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,7 +1879,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Ohävdad.</t>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1993,60 +1890,65 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1428309</v>
+        <v>16751274</v>
       </c>
       <c r="B13" t="n">
-        <v>86133</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4377</v>
+        <v>805</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505178.7975747958</v>
+        <v>505109</v>
       </c>
       <c r="R13" t="n">
-        <v>6338068.743390153</v>
+        <v>6338025</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2070,22 +1972,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,13 +1986,9 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Ohävdad.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2110,60 +1998,65 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1649101</v>
+        <v>16751275</v>
       </c>
       <c r="B14" t="n">
-        <v>86105</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4385</v>
+        <v>805</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Broskvaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gliophorus laetus</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Herink</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505178.7975747958</v>
+        <v>505161</v>
       </c>
       <c r="R14" t="n">
-        <v>6338068.743390153</v>
+        <v>6338073</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2187,22 +2080,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,13 +2094,9 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Ohävdad.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2227,56 +2106,65 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1247438</v>
+        <v>16751277</v>
       </c>
       <c r="B15" t="n">
-        <v>86319</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4398</v>
+        <v>805</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kålsboda, Sm</t>
+          <t>kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505178.7975747958</v>
+        <v>505156</v>
       </c>
       <c r="R15" t="n">
-        <v>6338068.743390153</v>
+        <v>6338061</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2300,22 +2188,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,13 +2202,9 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Ohävdad.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2340,60 +2214,65 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1347788</v>
+        <v>16751293</v>
       </c>
       <c r="B16" t="n">
-        <v>86131</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4374</v>
+        <v>805</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kålsboda, Sm</t>
+          <t>kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505178.7975747958</v>
+        <v>505185</v>
       </c>
       <c r="R16" t="n">
-        <v>6338068.743390153</v>
+        <v>6338080</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,22 +2296,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,13 +2310,9 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Ohävdad.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2457,60 +2322,65 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2365307</v>
+        <v>16751295</v>
       </c>
       <c r="B17" t="n">
-        <v>104837</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219955</v>
+        <v>805</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kålsboda, Sm</t>
+          <t>kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505178.7975747958</v>
+        <v>505191</v>
       </c>
       <c r="R17" t="n">
-        <v>6338068.743390153</v>
+        <v>6338087</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2534,22 +2404,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,13 +2418,9 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Ohävdad.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2574,60 +2430,65 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1615668</v>
+        <v>16751298</v>
       </c>
       <c r="B18" t="n">
-        <v>86147</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4383</v>
+        <v>805</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Småvaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hygrocybe insipida</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(J.E.Lange) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kålsboda, Sm</t>
+          <t>kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505178.7975747958</v>
+        <v>505120</v>
       </c>
       <c r="R18" t="n">
-        <v>6338068.743390153</v>
+        <v>6338099</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2651,22 +2512,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2675,13 +2526,9 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Ohävdad.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2691,60 +2538,65 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1275975</v>
+        <v>16751398</v>
       </c>
       <c r="B19" t="n">
-        <v>86130</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4373</v>
+        <v>805</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spröd vaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrocybe ceracea</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kålsboda, Sm</t>
+          <t>kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505178.7975747958</v>
+        <v>505178</v>
       </c>
       <c r="R19" t="n">
-        <v>6338068.743390153</v>
+        <v>6338066</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2768,22 +2620,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2792,13 +2634,9 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Ohävdad.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2815,43 +2653,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13393183</v>
+        <v>263733</v>
       </c>
       <c r="B20" t="n">
-        <v>44174</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89105</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102421</v>
+        <v>806</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slåttergubbemal</t>
+          <t>Luktvaxing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Digitivalva arnicella</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(von Heyden, 1863)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>mina</t>
+          <t>(Kühner) Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2860,13 +2697,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505178.7975747958</v>
+        <v>505219</v>
       </c>
       <c r="R20" t="n">
-        <v>6338068.743390153</v>
+        <v>6338034</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2893,26 +2730,11 @@
           <t>2007-10-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2007-10-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>smala nya minor på blad, nya generationen! Arten övervintrar som larv!</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2922,6 +2744,12 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Ohävdad.</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2937,42 +2765,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>328191</v>
+        <v>264386</v>
       </c>
       <c r="B21" t="n">
-        <v>86156</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89105</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Luktvaxing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>(Kühner) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2986,10 +2809,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505192.3401106596</v>
+        <v>505213</v>
       </c>
       <c r="R21" t="n">
-        <v>6338094.230286291</v>
+        <v>6338053</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3019,19 +2842,9 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3063,42 +2876,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>327984</v>
+        <v>264387</v>
       </c>
       <c r="B22" t="n">
-        <v>86156</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89105</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Luktvaxing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>(Kühner) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3112,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505182.082744967</v>
+        <v>505168</v>
       </c>
       <c r="R22" t="n">
-        <v>6338047.070924981</v>
+        <v>6338057</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,19 +2953,9 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3192,12 +2990,7 @@
         <v>264388</v>
       </c>
       <c r="B23" t="n">
-        <v>86159</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89105</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3209,7 +3002,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Luktvaxing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3238,10 +3031,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505157.6340404297</v>
+        <v>505158</v>
       </c>
       <c r="R23" t="n">
-        <v>6338058.420478748</v>
+        <v>6338058</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3271,19 +3064,9 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3315,42 +3098,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>301907</v>
+        <v>264389</v>
       </c>
       <c r="B24" t="n">
-        <v>86148</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89105</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådvaxskivling</t>
+          <t>Luktvaxing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrocybe intermedia</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pass.) Fayod</t>
+          <t>(Kühner) Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3364,10 +3142,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505204.3007672811</v>
+        <v>505155</v>
       </c>
       <c r="R24" t="n">
-        <v>6338082.323334695</v>
+        <v>6338062</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3397,19 +3175,9 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3441,15 +3209,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1221614</v>
+        <v>264390</v>
       </c>
       <c r="B25" t="n">
-        <v>86160</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89105</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,37 +3220,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4394</v>
+        <v>806</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Honungsvaxskivling</t>
+          <t>Luktvaxing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kühner</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Kühner) Singer</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505178.7975747958</v>
+        <v>505174</v>
       </c>
       <c r="R25" t="n">
-        <v>6338068.743390153</v>
+        <v>6338070</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3514,19 +3286,9 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3558,15 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1629781</v>
+        <v>265547</v>
       </c>
       <c r="B26" t="n">
-        <v>86104</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89105</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3574,37 +3331,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4384</v>
+        <v>806</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grå vaxskivling</t>
+          <t>Luktvaxing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gliophorus irrigatus</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) A.M.Ainsw. &amp; P.M.Kirk</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Kühner) Singer</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505178.7975747958</v>
+        <v>505153</v>
       </c>
       <c r="R26" t="n">
-        <v>6338068.743390153</v>
+        <v>6338063</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3628,22 +3394,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3675,42 +3431,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>264387</v>
+        <v>272231</v>
       </c>
       <c r="B27" t="n">
-        <v>86159</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89111</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
+          <t>Hygrocybe splendidissima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kühner) Singer</t>
+          <t>(P.D.Orton) M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3724,10 +3475,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505167.9528232142</v>
+        <v>505204</v>
       </c>
       <c r="R27" t="n">
-        <v>6338056.807662056</v>
+        <v>6338075</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3754,22 +3505,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3801,47 +3542,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>301908</v>
+        <v>594126</v>
       </c>
       <c r="B28" t="n">
-        <v>86148</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>801</v>
+        <v>1560</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådvaxskivling</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hygrocybe intermedia</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pass.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3850,10 +3586,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505202.7026057955</v>
+        <v>505135</v>
       </c>
       <c r="R28" t="n">
-        <v>6338057.935218746</v>
+        <v>6338106</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3880,22 +3616,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3907,9 +3633,14 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Ohävdad ängsmark</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3920,54 +3651,49 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>264390</v>
+        <v>594127</v>
       </c>
       <c r="B29" t="n">
-        <v>86159</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>806</v>
+        <v>1560</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kühner) Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3976,10 +3702,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505174.4523325279</v>
+        <v>505147</v>
       </c>
       <c r="R29" t="n">
-        <v>6338069.821758318</v>
+        <v>6338128</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4006,22 +3732,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4033,9 +3749,14 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Ohävdad ängsmark</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4046,22 +3767,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>264386</v>
+        <v>1275975</v>
       </c>
       <c r="B30" t="n">
-        <v>86159</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,46 +3785,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>806</v>
+        <v>4373</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Sprödvaxing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
+          <t>Hygrocybe ceracea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kühner) Singer</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Wulfen) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505213.0255209357</v>
+        <v>505179</v>
       </c>
       <c r="R30" t="n">
-        <v>6338053.071028022</v>
+        <v>6338069</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4132,22 +3839,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4161,7 +3858,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Ohävdad ängsmark</t>
+          <t>Ohävdad.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4172,22 +3869,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>264389</v>
+        <v>1347788</v>
       </c>
       <c r="B31" t="n">
-        <v>86159</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4195,46 +3887,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>806</v>
+        <v>4374</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kühner) Singer</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505154.9150403624</v>
+        <v>505179</v>
       </c>
       <c r="R31" t="n">
-        <v>6338061.668564037</v>
+        <v>6338069</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4258,22 +3941,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4287,7 +3960,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Ohävdad ängsmark</t>
+          <t>Ohävdad.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4298,69 +3971,55 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13682345</v>
+        <v>1428309</v>
       </c>
       <c r="B32" t="n">
-        <v>44174</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102421</v>
+        <v>4377</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slåttergubbemal</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Digitivalva arnicella</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(von Heyden, 1863)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>mina</t>
-        </is>
-      </c>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505182.6046048929</v>
+        <v>505179</v>
       </c>
       <c r="R32" t="n">
-        <v>6338063.870952405</v>
+        <v>6338069</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4384,27 +4043,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ohävdad ängsmark</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4418,7 +4062,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Ängs- och betesmark</t>
+          <t>Ohävdad.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4429,66 +4073,54 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>314697</v>
+        <v>16751300</v>
       </c>
       <c r="B33" t="n">
-        <v>86117</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>804</v>
+        <v>4377</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sepiavaxskivling</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neohygrocybe ovina</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bull.) Herink</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kålsboda, Sm</t>
+          <t>kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>505190.7630444193</v>
+        <v>505175</v>
       </c>
       <c r="R33" t="n">
-        <v>6338053.042924959</v>
+        <v>6338068</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4515,22 +4147,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4539,13 +4161,9 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Ohävdad ängsmark</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4562,62 +4180,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>284575</v>
+        <v>1549630</v>
       </c>
       <c r="B34" t="n">
-        <v>86127</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>793</v>
+        <v>4379</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fager vaxskivling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrocybe aurantiosplendens</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>R.Haller Aar.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>505190.7541703281</v>
+        <v>505179</v>
       </c>
       <c r="R34" t="n">
-        <v>6338060.087809531</v>
+        <v>6338069</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4641,22 +4245,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4670,10 +4264,9 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Ohävdad ängsmark</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr"/>
+          <t>Ohävdad.</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4682,69 +4275,55 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>272231</v>
+        <v>1615668</v>
       </c>
       <c r="B35" t="n">
-        <v>86165</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89096</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>809</v>
+        <v>4383</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Praktvaxskivling</t>
+          <t>Småvaxing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hygrocybe splendidissima</t>
+          <t>Hygrocybe insipida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.D.Orton) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(J.E.Lange) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>505203.7666802477</v>
+        <v>505179</v>
       </c>
       <c r="R35" t="n">
-        <v>6338075.27780225</v>
+        <v>6338069</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4768,22 +4347,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4797,7 +4366,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Ohävdad ängsmark</t>
+          <t>Ohävdad.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4808,69 +4377,55 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>329371</v>
+        <v>1629781</v>
       </c>
       <c r="B36" t="n">
-        <v>86156</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89054</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>805</v>
+        <v>4384</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Gråvaxing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Gliophorus irrigatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) A.M.Ainsw. &amp; P.M.Kirk</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505204.2987140662</v>
+        <v>505179</v>
       </c>
       <c r="R36" t="n">
-        <v>6338083.94906685</v>
+        <v>6338069</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4894,22 +4449,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4941,62 +4486,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>13682337</v>
+        <v>1649101</v>
       </c>
       <c r="B37" t="n">
-        <v>44174</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89055</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102421</v>
+        <v>4385</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slåttergubbemal</t>
+          <t>Broskvaxing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Digitivalva arnicella</t>
+          <t>Gliophorus laetus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(von Heyden, 1863)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>mina</t>
-        </is>
-      </c>
+          <t>(Pers.) Herink</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505157.6340404297</v>
+        <v>505179</v>
       </c>
       <c r="R37" t="n">
-        <v>6338058.420478748</v>
+        <v>6338069</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5020,27 +4551,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ohävdad ängsmark</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5054,7 +4570,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Ängs- och betesmark</t>
+          <t>Ohävdad.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5065,69 +4581,55 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13682336</v>
+        <v>1686351</v>
       </c>
       <c r="B38" t="n">
-        <v>44174</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102421</v>
+        <v>4388</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slåttergubbemal</t>
+          <t>Mönjevaxing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Digitivalva arnicella</t>
+          <t>Hygrocybe miniata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(von Heyden, 1863)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>mina</t>
-        </is>
-      </c>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505213.0255209357</v>
+        <v>505179</v>
       </c>
       <c r="R38" t="n">
-        <v>6338053.071028022</v>
+        <v>6338069</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5151,27 +4653,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ohävdad ängsmark</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5185,7 +4672,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Ängs- och betesmark</t>
+          <t>Ohävdad.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5196,66 +4683,50 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13682338</v>
+        <v>16751301</v>
       </c>
       <c r="B39" t="n">
-        <v>44174</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102421</v>
+        <v>4392</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slåttergubbemal</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Digitivalva arnicella</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(von Heyden, 1863)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>mina</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kålsboda, Sm</t>
+          <t>kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505174.4523325279</v>
+        <v>505175</v>
       </c>
       <c r="R39" t="n">
-        <v>6338069.821758318</v>
+        <v>6338068</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5282,27 +4753,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ohävdad ängsmark</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5311,13 +4767,9 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Ängs- och betesmark</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5334,62 +4786,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>329375</v>
+        <v>1209179</v>
       </c>
       <c r="B40" t="n">
-        <v>86156</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89059</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>805</v>
+        <v>4393</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Herink</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505111.5265675479</v>
+        <v>505179</v>
       </c>
       <c r="R40" t="n">
-        <v>6338020.970738455</v>
+        <v>6338069</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5413,22 +4851,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5442,7 +4870,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Ohävdad ängsmark</t>
+          <t>Ohävdad.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5453,22 +4881,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>265547</v>
+        <v>1221614</v>
       </c>
       <c r="B41" t="n">
-        <v>86159</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89106</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5476,46 +4899,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>806</v>
+        <v>4394</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Kühner) Singer</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>505152.7417407384</v>
+        <v>505179</v>
       </c>
       <c r="R41" t="n">
-        <v>6338062.749674516</v>
+        <v>6338069</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5539,22 +4953,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5586,59 +4990,47 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>329374</v>
+        <v>16751304</v>
       </c>
       <c r="B42" t="n">
-        <v>86156</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89106</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>805</v>
+        <v>4394</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kålsboda, Sm</t>
+          <t>kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>505182.6046048929</v>
+        <v>505175</v>
       </c>
       <c r="R42" t="n">
-        <v>6338063.870952405</v>
+        <v>6338068</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5665,22 +5057,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2008-10-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5689,13 +5071,9 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Ohävdad ängsmark</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5712,59 +5090,41 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>14197202</v>
+        <v>1247438</v>
       </c>
       <c r="B43" t="n">
-        <v>39526</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101060</v>
+        <v>4398</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svävflugedagsvärmare</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hemaris tityus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505178.7975747958</v>
+        <v>505179</v>
       </c>
       <c r="R43" t="n">
-        <v>6338068.743390153</v>
+        <v>6338069</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5791,22 +5151,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2009-06-26</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2009-06-26</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5817,6 +5167,11 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Ohävdad.</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5826,26 +5181,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Hugo Ivarsson, Alfred Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>15487977</v>
+        <v>13368999</v>
       </c>
       <c r="B44" t="n">
-        <v>27696</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>26894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,20 +5216,29 @@
           <t>(Horváth, 1881)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505178.7975747958</v>
+        <v>505135</v>
       </c>
       <c r="R44" t="n">
-        <v>6338068.743390153</v>
+        <v>6338106</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5907,32 +5262,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AD44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5949,63 +5299,62 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16751398</v>
+        <v>13562875</v>
       </c>
       <c r="B45" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45046</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>805</v>
+        <v>102020</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>kålsboda, Sm</t>
+          <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505177.7150090067</v>
+        <v>505209</v>
       </c>
       <c r="R45" t="n">
-        <v>6338066.032461601</v>
+        <v>6338039</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6029,22 +5378,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ny artfynd för länet</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6053,82 +5397,76 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Tid. betesmark</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Via Ekologa /Jonas Wäglind</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>16751295</v>
+        <v>13380116</v>
       </c>
       <c r="B46" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>805</v>
+        <v>102021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>kålsboda, Sm</t>
+          <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505191.2630220242</v>
+        <v>505179</v>
       </c>
       <c r="R46" t="n">
-        <v>6338087.184091629</v>
+        <v>6338069</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6152,22 +5490,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6176,7 +5504,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6188,67 +5515,61 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16751293</v>
+        <v>13368975</v>
       </c>
       <c r="B47" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44889</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>805</v>
+        <v>102421</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Slåttergubbemal</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Digitivalva arnicella</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>(von Heyden, 1863)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>mina</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>kålsboda, Sm</t>
+          <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505184.7560930523</v>
+        <v>505223</v>
       </c>
       <c r="R47" t="n">
-        <v>6338080.131049836</v>
+        <v>6338041</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6275,22 +5596,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6299,9 +5610,13 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>ohävdad betesmark</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6311,62 +5626,60 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16751302</v>
+        <v>13393183</v>
       </c>
       <c r="B48" t="n">
-        <v>86130</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44889</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>239209</v>
+        <v>102421</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kantarellvaxskivling</t>
+          <t>Slåttergubbemal</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Digitivalva arnicella</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(von Heyden, 1863)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>mina</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>kålsboda, Sm</t>
+          <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505174.9980397507</v>
+        <v>505179</v>
       </c>
       <c r="R48" t="n">
-        <v>6338067.654789772</v>
+        <v>6338069</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6390,22 +5703,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>smala nya minor på blad, nya generationen! Arten övervintrar som larv!</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6414,7 +5722,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6426,22 +5733,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>16751296</v>
+        <v>13682336</v>
       </c>
       <c r="B49" t="n">
-        <v>44175</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44889</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6468,32 +5770,24 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>mina</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>kålsboda, Sm</t>
+          <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>505184.1633408091</v>
+        <v>505213</v>
       </c>
       <c r="R49" t="n">
-        <v>6338119.689688629</v>
+        <v>6338053</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6520,22 +5814,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6546,6 +5835,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Ängs- och betesmark</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6562,52 +5856,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>16751300</v>
+        <v>13682337</v>
       </c>
       <c r="B50" t="n">
-        <v>86134</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44889</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4377</v>
+        <v>102421</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Slåttergubbemal</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Digitivalva arnicella</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>(von Heyden, 1863)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>mina</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>kålsboda, Sm</t>
+          <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505174.9980397507</v>
+        <v>505158</v>
       </c>
       <c r="R50" t="n">
-        <v>6338067.654789772</v>
+        <v>6338058</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6634,22 +5930,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6658,9 +5949,13 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Ängs- och betesmark</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6677,15 +5972,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>16751292</v>
+        <v>13682338</v>
       </c>
       <c r="B51" t="n">
-        <v>44175</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44889</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6712,32 +6002,24 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>mina</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kålsboda, Sm</t>
+          <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>505177.7150090067</v>
+        <v>505174</v>
       </c>
       <c r="R51" t="n">
-        <v>6338066.032461601</v>
+        <v>6338070</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6764,22 +6046,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-10</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6790,6 +6067,11 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Ängs- och betesmark</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6806,52 +6088,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>16751304</v>
+        <v>13682345</v>
       </c>
       <c r="B52" t="n">
-        <v>86161</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44889</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4394</v>
+        <v>102421</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Honungsvaxskivling</t>
+          <t>Slåttergubbemal</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Digitivalva arnicella</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kühner</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+          <t>(von Heyden, 1863)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>mina</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>kålsboda, Sm</t>
+          <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>505174.9980397507</v>
+        <v>505183</v>
       </c>
       <c r="R52" t="n">
-        <v>6338067.654789772</v>
+        <v>6338064</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6878,22 +6162,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-03</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ohävdad ängsmark</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6902,9 +6181,13 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Ängs- och betesmark</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6921,48 +6204,62 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>16751301</v>
+        <v>16751292</v>
       </c>
       <c r="B53" t="n">
-        <v>86314</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44889</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4392</v>
+        <v>102421</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Slåttergubbemal</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>Digitivalva arnicella</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(von Heyden, 1863)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>mina</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>505174.9980397507</v>
+        <v>505178</v>
       </c>
       <c r="R53" t="n">
-        <v>6338067.654789772</v>
+        <v>6338066</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6992,28 +6289,17 @@
           <t>2014-09-29</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2014-09-29</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7032,60 +6318,62 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>16751275</v>
+        <v>16751296</v>
       </c>
       <c r="B54" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44889</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>805</v>
+        <v>102421</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Slåttergubbemal</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Digitivalva arnicella</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>(von Heyden, 1863)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>mina</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kålsboda, Sm</t>
+          <t>kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>505161.4172981796</v>
+        <v>505184</v>
       </c>
       <c r="R54" t="n">
-        <v>6338072.514976528</v>
+        <v>6338120</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7115,28 +6403,17 @@
           <t>2014-09-29</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2014-09-29</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7155,63 +6432,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>16751277</v>
+        <v>14196220</v>
       </c>
       <c r="B55" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43378</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>805</v>
+        <v>201075</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>kålsboda, Sm</t>
+          <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>505156.0023686544</v>
+        <v>505179</v>
       </c>
       <c r="R55" t="n">
-        <v>6338060.586095488</v>
+        <v>6338069</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7235,22 +6502,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7259,7 +6516,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7271,74 +6527,64 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Tobias Ivarsson, Hugo Ivarsson, Alfred Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>13562875</v>
+        <v>13380119</v>
       </c>
       <c r="B56" t="n">
-        <v>44332</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>43285</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102020</v>
+        <v>201143</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>505209.2424216498</v>
+        <v>505179</v>
       </c>
       <c r="R56" t="n">
-        <v>6338038.976416338</v>
+        <v>6338069</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7362,27 +6608,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ny artfynd för länet</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7393,62 +6624,66 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Tid. betesmark</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ekologa /Jonas Wäglind</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Via Ekologa /Jonas Wäglind</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>74437154</v>
+        <v>14197023</v>
       </c>
       <c r="B57" t="n">
-        <v>105898</v>
+        <v>43309</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221447</v>
+        <v>201146</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kålsboda 150 m S, Sm</t>
+          <t>Kålsboda, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>505239</v>
+        <v>505179</v>
       </c>
       <c r="R57" t="n">
-        <v>6338020</v>
+        <v>6338069</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -7475,17 +6710,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>2009-06-26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5F8b 0115. SOM: Gentianella campestris. LEG: Sven-Åke Svensson</t>
+          <t>2009-06-26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7496,26 +6726,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Något fuktig, ogödslad hage</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
+          <t>Tobias Ivarsson, Alfred Ivarsson, Hugo Ivarsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>Smålands flora (1978-2007)</t>
+          <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
     </row>
@@ -7524,7 +6749,7 @@
         <v>74468389</v>
       </c>
       <c r="B58" t="n">
-        <v>98671</v>
+        <v>99120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7629,6 +6854,621 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2365307</v>
+      </c>
+      <c r="B59" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kålsboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>505179</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6338069</v>
+      </c>
+      <c r="S59" t="n">
+        <v>50</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Ohävdad.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2674357</v>
+      </c>
+      <c r="B60" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kålsboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>505179</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6338069</v>
+      </c>
+      <c r="S60" t="n">
+        <v>50</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Ohävdad.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2649255</v>
+      </c>
+      <c r="B61" t="n">
+        <v>109866</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kålsboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>505179</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6338069</v>
+      </c>
+      <c r="S61" t="n">
+        <v>50</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Ohävdad.</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>74437152</v>
+      </c>
+      <c r="B62" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kålsboda 150 m S, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>505239</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6338020</v>
+      </c>
+      <c r="S62" t="n">
+        <v>50</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5F8b 0115. SOM: Gentianella campestris. LEG: Sven-Åke Svensson. KOM: 10 plantor</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Något fuktig, ogödslad hage</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>6673484</v>
+      </c>
+      <c r="B63" t="n">
+        <v>89079</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kålsboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>505179</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6338069</v>
+      </c>
+      <c r="S63" t="n">
+        <v>50</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2007-10-02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2007-10-02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Ohävdad.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>16751302</v>
+      </c>
+      <c r="B64" t="n">
+        <v>89079</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>kålsboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>505175</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6338068</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2014-09-29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2014-09-29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
